--- a/data/trans_dic/P79$impuestos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P79$impuestos_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,52</t>
+          <t>0,57; 2,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,05</t>
+          <t>0,5; 2,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,95</t>
+          <t>0,69; 2,07</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,59</t>
+          <t>0,45; 1,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,31</t>
+          <t>0,9; 2,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,6</t>
+          <t>0,82; 1,72</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,6</t>
+          <t>0,74; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,1</t>
+          <t>0,96; 2,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,93</t>
+          <t>1,01; 2,23</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,99</t>
+          <t>1,1; 3,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,32</t>
+          <t>0,48; 1,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,92</t>
+          <t>0,88; 1,96</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,76</t>
+          <t>1,0; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,53</t>
+          <t>0,93; 1,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,47</t>
+          <t>1,07; 1,63</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>16918</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3432; 15541</t>
+          <t>3847; 18308</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3407; 14500</t>
+          <t>3575; 16911</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8740; 25857</t>
+          <t>9538; 28629</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>24942</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3973; 18645</t>
+          <t>4588; 18582</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8582; 21340</t>
+          <t>9297; 22814</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14610; 33567</t>
+          <t>16770; 35335</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>23225</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5156; 17605</t>
+          <t>5705; 19751</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4172; 18937</t>
+          <t>7456; 20143</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11640; 30526</t>
+          <t>15527; 34494</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>26328</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8738; 26880</t>
+          <t>10539; 31086</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4620; 13017</t>
+          <t>5134; 15027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16382; 36275</t>
+          <t>18011; 39870</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30468; 59263</t>
+          <t>34229; 63593</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28652; 53784</t>
+          <t>33638; 58000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64779; 100895</t>
+          <t>75265; 114533</t>
         </is>
       </c>
     </row>
